--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_42.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2652601.092855884</v>
+        <v>2645623.708163758</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979919</v>
+        <v>9956801.353979921</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979919</v>
+        <v>9956801.353979921</v>
       </c>
     </row>
     <row r="9">
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>26.34349040625725</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>18.33383170272989</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -739,22 +739,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>251.9723814019027</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>185.9212948591247</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>421</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100.3331446583043</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
@@ -909,10 +909,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>176.4246500889419</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -979,19 +979,19 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>160.6175271261213</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1021,10 +1021,10 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>198.5500884730067</v>
+        <v>421</v>
       </c>
       <c r="T6" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>22.09120398974605</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>263.2631591877375</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>125.5575371970016</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>174.0125335238739</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97.23431917176916</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1504,7 +1504,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V12" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W12" t="n">
         <v>82.37314290982852</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>277.7834726314007</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S15" t="n">
         <v>116.5639999646113</v>
@@ -1738,13 +1738,13 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V15" t="n">
         <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>69.86273944538755</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T17" t="n">
         <v>236.6755817285639</v>
@@ -1966,10 +1966,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>547.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S18" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T18" t="n">
         <v>55.35776521751382</v>
@@ -1978,7 +1978,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V18" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>82.37314290982852</v>
@@ -2091,7 +2091,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
         <v>58.00965870352741</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2158,7 +2158,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>84.14143263308497</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2221,10 +2221,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="22">
@@ -2328,13 +2328,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H23" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T24" t="n">
         <v>55.35776521751382</v>
@@ -2455,13 +2455,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>82.37314290982852</v>
+        <v>145.0509054352709</v>
       </c>
       <c r="X24" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>288.9898902010971</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S26" t="n">
         <v>144.8481678023229</v>
@@ -2607,7 +2607,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>279.8510241668239</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
@@ -2686,16 +2686,16 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U27" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V27" t="n">
         <v>64.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>82.37314290982852</v>
+        <v>145.050905435271</v>
       </c>
       <c r="X27" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
         <v>49.39139276613435</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>236.6755817285639</v>
@@ -2872,10 +2872,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>70.00566530352997</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
         <v>55.35776521751382</v>
@@ -3045,7 +3045,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T32" t="n">
         <v>236.6755817285639</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>274.1550540812894</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>11.09991244551929</v>
+        <v>91.60958778454074</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>197.2737972923793</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>242.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>165.2828240682209</v>
+        <v>161.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.55655664632661</v>
+        <v>97.2343191717691</v>
       </c>
       <c r="C36" t="n">
         <v>11.09991244551929</v>
@@ -3349,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3580,7 +3580,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>62.67776252544254</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>49.39139276613435</v>
+        <v>122.4329129537</v>
       </c>
     </row>
     <row r="40">
@@ -3753,7 +3753,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>270.3153174799449</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429563</v>
       </c>
       <c r="U42" t="n">
         <v>50.21035976018675</v>
@@ -3990,10 +3990,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176904</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4108,13 +4108,13 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
         <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>69.86273944538755</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.4463380542246</v>
+        <v>266.9273161322752</v>
       </c>
       <c r="C2" t="n">
-        <v>235.472016596655</v>
+        <v>216.9529946747056</v>
       </c>
       <c r="D2" t="n">
-        <v>225.028424940241</v>
+        <v>206.5094030182917</v>
       </c>
       <c r="E2" t="n">
-        <v>220.6210617009798</v>
+        <v>202.1020397790304</v>
       </c>
       <c r="F2" t="n">
-        <v>215.6820428039981</v>
+        <v>197.1630208820488</v>
       </c>
       <c r="G2" t="n">
-        <v>211.8867172615575</v>
+        <v>193.3676953396081</v>
       </c>
       <c r="H2" t="n">
         <v>185.2771309926108</v>
@@ -4321,52 +4321,52 @@
         <v>33.68</v>
       </c>
       <c r="J2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="K2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="L2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="M2" t="n">
-        <v>450.47</v>
+        <v>841.7791130376559</v>
       </c>
       <c r="N2" t="n">
-        <v>850.4200000000001</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="O2" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="P2" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1684</v>
+        <v>1665.480978078051</v>
       </c>
       <c r="S2" t="n">
-        <v>1588.193769896644</v>
+        <v>1569.674747974694</v>
       </c>
       <c r="T2" t="n">
-        <v>1399.632576231427</v>
+        <v>1381.113554309478</v>
       </c>
       <c r="U2" t="n">
-        <v>1147.893892848992</v>
+        <v>1129.374870927043</v>
       </c>
       <c r="V2" t="n">
-        <v>915.7211411653319</v>
+        <v>897.2021192433824</v>
       </c>
       <c r="W2" t="n">
-        <v>674.9398522956878</v>
+        <v>656.4208303737385</v>
       </c>
       <c r="X2" t="n">
-        <v>480.7157780929932</v>
+        <v>462.1967561710438</v>
       </c>
       <c r="Y2" t="n">
-        <v>368.2739268982392</v>
+        <v>349.7549049762899</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>507.5171386800518</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C3" t="n">
-        <v>507.5171386800518</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="D3" t="n">
-        <v>252.9995817084329</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="E3" t="n">
-        <v>252.9995817084329</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="F3" t="n">
-        <v>252.9995817084329</v>
+        <v>557.002608126814</v>
       </c>
       <c r="G3" t="n">
-        <v>252.9995817084329</v>
+        <v>557.002608126814</v>
       </c>
       <c r="H3" t="n">
-        <v>252.9995817084329</v>
+        <v>221.4792877364897</v>
       </c>
       <c r="I3" t="n">
         <v>33.68</v>
@@ -4439,13 +4439,13 @@
         <v>952.8330371097362</v>
       </c>
       <c r="W3" t="n">
-        <v>527.5805118572109</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>507.5171386800518</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y3" t="n">
-        <v>507.5171386800518</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1183.403502424373</v>
+        <v>484.5438078492905</v>
       </c>
       <c r="C4" t="n">
-        <v>1183.403502424373</v>
+        <v>610.5458136677263</v>
       </c>
       <c r="D4" t="n">
-        <v>1183.403502424373</v>
+        <v>723.8649577927264</v>
       </c>
       <c r="E4" t="n">
-        <v>1183.403502424373</v>
+        <v>723.8649577927264</v>
       </c>
       <c r="F4" t="n">
-        <v>1183.403502424373</v>
+        <v>848.2259303846619</v>
       </c>
       <c r="G4" t="n">
-        <v>1183.403502424373</v>
+        <v>1001.632496271547</v>
       </c>
       <c r="H4" t="n">
-        <v>1183.403502424373</v>
+        <v>1171.149081430945</v>
       </c>
       <c r="I4" t="n">
-        <v>1183.403502424373</v>
+        <v>1392.281960367028</v>
       </c>
       <c r="J4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T4" t="n">
-        <v>259.005934252978</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>505.5571268912646</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="V4" t="n">
-        <v>704.3785197772106</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="W4" t="n">
-        <v>876.269438036888</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="X4" t="n">
-        <v>1027.300229061082</v>
+        <v>372.7864701829984</v>
       </c>
       <c r="Y4" t="n">
-        <v>1138.709529740114</v>
+        <v>372.7864701829984</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.9273161322752</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>216.9529946747056</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D5" t="n">
-        <v>206.5094030182917</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E5" t="n">
-        <v>202.1020397790304</v>
+        <v>220.6210617009798</v>
       </c>
       <c r="F5" t="n">
-        <v>197.1630208820488</v>
+        <v>215.6820428039981</v>
       </c>
       <c r="G5" t="n">
-        <v>193.3676953396081</v>
+        <v>211.8867172615575</v>
       </c>
       <c r="H5" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I5" t="n">
         <v>33.68</v>
@@ -4573,10 +4573,10 @@
         <v>1258.569113037656</v>
       </c>
       <c r="O5" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="P5" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>362.7098342171994</v>
+        <v>542.053357927307</v>
       </c>
       <c r="C6" t="n">
-        <v>362.7098342171994</v>
+        <v>542.053357927307</v>
       </c>
       <c r="D6" t="n">
-        <v>362.7098342171994</v>
+        <v>542.053357927307</v>
       </c>
       <c r="E6" t="n">
-        <v>362.7098342171994</v>
+        <v>195.9199263900215</v>
       </c>
       <c r="F6" t="n">
-        <v>362.7098342171994</v>
+        <v>195.9199263900215</v>
       </c>
       <c r="G6" t="n">
-        <v>33.68</v>
+        <v>195.9199263900215</v>
       </c>
       <c r="H6" t="n">
-        <v>33.68</v>
+        <v>195.9199263900215</v>
       </c>
       <c r="I6" t="n">
         <v>33.68</v>
@@ -4664,25 +4664,25 @@
         <v>1040.351008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>839.7953640398628</v>
+        <v>615.0984837095665</v>
       </c>
       <c r="T6" t="n">
-        <v>430.343075941364</v>
+        <v>609.6865996514717</v>
       </c>
       <c r="U6" t="n">
-        <v>430.1305913351147</v>
+        <v>609.4741150452224</v>
       </c>
       <c r="V6" t="n">
-        <v>415.4733517477206</v>
+        <v>594.8168754578284</v>
       </c>
       <c r="W6" t="n">
-        <v>382.7732073943585</v>
+        <v>562.1167311044662</v>
       </c>
       <c r="X6" t="n">
-        <v>362.7098342171994</v>
+        <v>542.053357927307</v>
       </c>
       <c r="Y6" t="n">
-        <v>362.7098342171994</v>
+        <v>542.053357927307</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.47201175835417</v>
+        <v>579.7683476291953</v>
       </c>
       <c r="C7" t="n">
-        <v>173.4740175767899</v>
+        <v>705.7703534476311</v>
       </c>
       <c r="D7" t="n">
-        <v>286.79316170179</v>
+        <v>819.0894975726312</v>
       </c>
       <c r="E7" t="n">
-        <v>404.6220659132031</v>
+        <v>936.9184017840442</v>
       </c>
       <c r="F7" t="n">
-        <v>528.9830385051386</v>
+        <v>1061.27937437598</v>
       </c>
       <c r="G7" t="n">
-        <v>682.3896043920238</v>
+        <v>1214.685940262865</v>
       </c>
       <c r="H7" t="n">
-        <v>851.9061895514213</v>
+        <v>1384.202525422263</v>
       </c>
       <c r="I7" t="n">
-        <v>1073.039068487504</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="J7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4755,13 +4755,13 @@
         <v>33.68</v>
       </c>
       <c r="W7" t="n">
-        <v>33.68</v>
+        <v>205.5709182596774</v>
       </c>
       <c r="X7" t="n">
-        <v>33.68</v>
+        <v>356.6017092838709</v>
       </c>
       <c r="Y7" t="n">
-        <v>33.68</v>
+        <v>468.0110099629032</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>285.4463380542246</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E8" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G8" t="n">
-        <v>193.3676953396081</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I8" t="n">
         <v>33.68</v>
@@ -4801,19 +4801,19 @@
         <v>424.9891130376557</v>
       </c>
       <c r="L8" t="n">
-        <v>841.7791130376557</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="M8" t="n">
+        <v>841.7791130376559</v>
+      </c>
+      <c r="N8" t="n">
         <v>1258.569113037656</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1675.359113037656</v>
       </c>
-      <c r="O8" t="n">
-        <v>1684</v>
-      </c>
       <c r="P8" t="n">
-        <v>1684</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="Q8" t="n">
         <v>1684</v>
@@ -4822,25 +4822,25 @@
         <v>1684</v>
       </c>
       <c r="S8" t="n">
-        <v>1588.193769896644</v>
+        <v>1418.077616982083</v>
       </c>
       <c r="T8" t="n">
-        <v>1399.632576231427</v>
+        <v>1229.516423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>1147.893892848992</v>
+        <v>977.7777399344324</v>
       </c>
       <c r="V8" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W8" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>480.7157780929932</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="C9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="D9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="E9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="F9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="G9" t="n">
         <v>369.2033203903244</v>
@@ -4895,31 +4895,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1014.284879873102</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>838.5146439904007</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>771.2782803897833</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T9" t="n">
-        <v>765.8663963316885</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>765.6539117254392</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V9" t="n">
-        <v>750.9966721380451</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W9" t="n">
-        <v>718.296527784683</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
       <c r="Y9" t="n">
-        <v>698.2331546075238</v>
+        <v>496.0291155388109</v>
       </c>
     </row>
     <row r="10">
@@ -4929,19 +4929,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1025.140933153428</v>
+        <v>1213.216612312233</v>
       </c>
       <c r="C10" t="n">
-        <v>1151.142938971864</v>
+        <v>1339.218618130669</v>
       </c>
       <c r="D10" t="n">
-        <v>1264.462083096864</v>
+        <v>1452.537762255669</v>
       </c>
       <c r="E10" t="n">
-        <v>1382.290987308277</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="F10" t="n">
-        <v>1506.651959900212</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="G10" t="n">
         <v>1544.487243076824</v>
@@ -4983,22 +4983,22 @@
         <v>33.68</v>
       </c>
       <c r="T10" t="n">
-        <v>33.68</v>
+        <v>221.7556791588049</v>
       </c>
       <c r="U10" t="n">
-        <v>280.2311926382866</v>
+        <v>468.3068717970915</v>
       </c>
       <c r="V10" t="n">
-        <v>479.0525855242326</v>
+        <v>667.1282646830375</v>
       </c>
       <c r="W10" t="n">
-        <v>650.94350378391</v>
+        <v>839.0191829427149</v>
       </c>
       <c r="X10" t="n">
-        <v>801.9742948081035</v>
+        <v>990.0499739669084</v>
       </c>
       <c r="Y10" t="n">
-        <v>913.3835954871358</v>
+        <v>1101.459274645941</v>
       </c>
     </row>
     <row r="11">
@@ -5038,19 +5038,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376558</v>
       </c>
       <c r="N11" t="n">
-        <v>1542.849113037656</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O11" t="n">
-        <v>2096.259113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P11" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>409.4673863086053</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S12" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X12" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y12" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="13">
@@ -5220,10 +5220,10 @@
         <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U13" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V13" t="n">
         <v>521.9574820108303</v>
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5272,22 +5272,22 @@
         <v>44.72</v>
       </c>
       <c r="K14" t="n">
-        <v>598.13</v>
+        <v>44.72</v>
       </c>
       <c r="L14" t="n">
-        <v>598.13</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M14" t="n">
-        <v>1108.978828728935</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N14" t="n">
-        <v>1662.388828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O14" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H15" t="n">
         <v>44.72</v>
@@ -5372,28 +5372,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>919.5630540741914</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>801.8216399685234</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>745.9047054053782</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U15" t="n">
-        <v>695.1871702940784</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V15" t="n">
-        <v>630.0248802016338</v>
+        <v>648.036913346663</v>
       </c>
       <c r="W15" t="n">
-        <v>546.8196853432211</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>476.2512616610114</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C16" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D16" t="n">
         <v>1010.366979583462</v>
@@ -5457,22 +5457,22 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W16" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X16" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="17">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
@@ -5509,19 +5509,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L17" t="n">
-        <v>436.0291130376557</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M17" t="n">
-        <v>946.8779417665908</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N17" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O17" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>1797.400904947332</v>
@@ -5533,25 +5533,25 @@
         <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5609,16 +5609,16 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>647.3506049216877</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S18" t="n">
-        <v>466.2983195781991</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T18" t="n">
-        <v>410.3813850150538</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U18" t="n">
-        <v>359.6638499037541</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V18" t="n">
         <v>294.5015598113094</v>
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
         <v>103.3156148520479</v>
@@ -5743,52 +5743,52 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>1108.978828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>1662.388828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>2215.798828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P20" t="n">
-        <v>2215.798828728935</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C21" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E21" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5864,10 +5864,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="22">
@@ -5971,34 +5971,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>64.92117127106515</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K23" t="n">
-        <v>618.3311712710652</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L23" t="n">
-        <v>1171.741171271065</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M23" t="n">
-        <v>1682.59</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N23" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O23" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
@@ -6080,28 +6080,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>708.3170038559392</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T24" t="n">
-        <v>652.400069292794</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U24" t="n">
-        <v>601.6825341814942</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V24" t="n">
-        <v>536.5202440890496</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W24" t="n">
-        <v>453.3150492306369</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>382.7466255484273</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
         <v>90.8376455473191</v>
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H25" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J25" t="n">
         <v>1860.696627021627</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6241,13 +6241,13 @@
         <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S26" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T26" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U26" t="n">
         <v>1544.373295489988</v>
@@ -6320,22 +6320,22 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U27" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V27" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W27" t="n">
-        <v>211.2963649528968</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X27" t="n">
         <v>140.7279412706871</v>
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C28" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D28" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E28" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F28" t="n">
         <v>1153.55685638681</v>
@@ -6405,22 +6405,22 @@
         <v>44.72</v>
       </c>
       <c r="T28" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U28" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X28" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y28" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="29">
@@ -6430,46 +6430,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L29" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M29" t="n">
-        <v>946.8779417665908</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N29" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O29" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>1797.400904947332</v>
@@ -6481,25 +6481,25 @@
         <v>2236</v>
       </c>
       <c r="S29" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,13 +6509,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C32" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D32" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E32" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G32" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
@@ -6694,22 +6694,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L32" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M32" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N32" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6718,25 +6718,25 @@
         <v>2236</v>
       </c>
       <c r="S32" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T32" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U32" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V32" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W32" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X32" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y32" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H33" t="n">
         <v>44.72</v>
@@ -6791,31 +6791,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T33" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>382.7466255484273</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y33" t="n">
-        <v>332.8563298250593</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="34">
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6931,22 +6931,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M35" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N35" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="O35" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6973,7 +6973,7 @@
         <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
         <v>44.72</v>
@@ -7052,7 +7052,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="37">
@@ -7071,16 +7071,16 @@
         <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I37" t="n">
         <v>1549.112886369176</v>
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7168,13 +7168,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M38" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N38" t="n">
         <v>1500.287941766591</v>
@@ -7189,28 +7189,28 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D39" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E39" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F39" t="n">
         <v>44.72</v>
@@ -7289,7 +7289,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="40">
@@ -7368,7 +7368,7 @@
         <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
         <v>44.72</v>
@@ -7405,19 +7405,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>1797.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>398.9989442256527</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>927.106645136268</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>809.3652310305999</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>753.4482964674547</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U42" t="n">
-        <v>702.730761356155</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V42" t="n">
-        <v>637.5684712637103</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W42" t="n">
-        <v>554.3632764052976</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X42" t="n">
-        <v>483.794852723088</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y42" t="n">
-        <v>433.9045569997199</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="43">
@@ -7536,31 +7536,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H43" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K43" t="n">
         <v>1921.561060958496</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7633,31 +7633,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>64.92117127106526</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K44" t="n">
-        <v>64.92117127106526</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L44" t="n">
-        <v>618.3311712710653</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="46">
@@ -7773,31 +7773,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K46" t="n">
         <v>1921.561060958496</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>965.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>881.2388570597343</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>9.015228689513952</v>
       </c>
       <c r="Q2" t="n">
-        <v>593.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8216,13 +8216,13 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>78.97603822292498</v>
+        <v>491.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>593.8226843274854</v>
+        <v>181.5508529763179</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>965.2621276423173</v>
@@ -8453,13 +8453,13 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>78.97603822292498</v>
+        <v>491.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>181.5508529763179</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,22 +8681,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>734.371980200822</v>
       </c>
       <c r="O11" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>141.4394711137563</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,10 +8915,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,13 +8927,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>90.65309308021877</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,7 +9152,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9161,13 +9161,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -9404,10 +9404,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q20" t="n">
-        <v>193.2279078336117</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>55.44822975121676</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10112,10 +10112,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P32" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,16 +10583,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
@@ -11048,7 +11048,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,13 +11057,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O41" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>55.44822975121687</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,13 +11297,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -26278,7 +26278,7 @@
         <v>1322345.892349224</v>
       </c>
       <c r="E2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="F2" t="n">
         <v>1322345.892349225</v>
@@ -26287,7 +26287,7 @@
         <v>1322345.892349225</v>
       </c>
       <c r="H2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="I2" t="n">
         <v>1322345.892349225</v>
@@ -26296,7 +26296,7 @@
         <v>1322345.892349225</v>
       </c>
       <c r="K2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="L2" t="n">
         <v>1322345.892349225</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743712</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505588</v>
+        <v>535094.4215636664</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983396</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>548574.5331067148</v>
+        <v>547011.9200132695</v>
       </c>
       <c r="C6" t="n">
-        <v>698799.0488702591</v>
+        <v>697236.435776814</v>
       </c>
       <c r="D6" t="n">
-        <v>700834.3218682975</v>
+        <v>699271.7087748526</v>
       </c>
       <c r="E6" t="n">
-        <v>387264.4891226889</v>
+        <v>385522.639309582</v>
       </c>
       <c r="F6" t="n">
-        <v>717783.3844681935</v>
+        <v>716041.5346550859</v>
       </c>
       <c r="G6" t="n">
-        <v>719728.960936379</v>
+        <v>717987.1111232715</v>
       </c>
       <c r="H6" t="n">
-        <v>721677.2377536801</v>
+        <v>719935.3879405732</v>
       </c>
       <c r="I6" t="n">
-        <v>723628.2343970408</v>
+        <v>721886.3845839329</v>
       </c>
       <c r="J6" t="n">
-        <v>297389.970598666</v>
+        <v>295648.1207855581</v>
       </c>
       <c r="K6" t="n">
-        <v>727538.4663508848</v>
+        <v>725796.6165377779</v>
       </c>
       <c r="L6" t="n">
-        <v>729497.7419111448</v>
+        <v>727755.8920980368</v>
       </c>
       <c r="M6" t="n">
-        <v>682883.8178071238</v>
+        <v>681141.9679940161</v>
       </c>
       <c r="N6" t="n">
-        <v>733424.7148419772</v>
+        <v>731682.8650288702</v>
       </c>
       <c r="O6" t="n">
-        <v>455392.4540997157</v>
+        <v>453650.6042866082</v>
       </c>
       <c r="P6" t="n">
-        <v>737363.0569507263</v>
+        <v>735621.2071376179</v>
       </c>
     </row>
   </sheetData>
@@ -26993,19 +26993,19 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K2" t="n">
         <v>-0</v>
       </c>
-      <c r="J2" t="n">
-        <v>350</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>-0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -27024,11 +27024,11 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
@@ -27036,10 +27036,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>-0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>232.5447671255646</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>95.9653054957999</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>31.20509103222381</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>11.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,31 +27591,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>332.2592272908755</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>189.0116586437827</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27758,19 +27758,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>56.50885876522722</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27800,10 +27800,10 @@
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>268.0139114916046</v>
+        <v>45.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>301.0451253455172</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27849,13 +27849,13 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>338.5372108267456</v>
       </c>
       <c r="J7" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>231.5850086145854</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28001,7 +28001,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>200.1819986780258</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>373.2612637685054</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28074,13 +28074,13 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>373.8591682926689</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>283.2613305956833</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>228.7711261016186</v>
@@ -28119,7 +28119,7 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28223,10 +28223,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28283,7 +28283,7 @@
         <v>350</v>
       </c>
       <c r="V12" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="W12" t="n">
         <v>350</v>
@@ -28356,13 +28356,13 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
       </c>
       <c r="V13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W13" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28478,7 +28478,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
@@ -28508,7 +28508,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="S15" t="n">
         <v>350</v>
@@ -28517,13 +28517,13 @@
         <v>350</v>
       </c>
       <c r="U15" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
       </c>
       <c r="W15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>350</v>
@@ -28545,7 +28545,7 @@
         <v>350</v>
       </c>
       <c r="D16" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E16" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28669,7 +28669,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T17" t="n">
         <v>350</v>
@@ -28745,10 +28745,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S18" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T18" t="n">
         <v>350</v>
@@ -28757,7 +28757,7 @@
         <v>350</v>
       </c>
       <c r="V18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>350</v>
@@ -28870,7 +28870,7 @@
         <v>350</v>
       </c>
       <c r="G20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H20" t="n">
         <v>350</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28937,7 +28937,7 @@
         <v>350</v>
       </c>
       <c r="C21" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -28946,7 +28946,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -29000,10 +29000,10 @@
         <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="22">
@@ -29107,13 +29107,13 @@
         <v>350</v>
       </c>
       <c r="G23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H23" t="n">
         <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29216,13 +29216,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
       </c>
       <c r="S24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>350</v>
@@ -29234,13 +29234,13 @@
         <v>350</v>
       </c>
       <c r="W24" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="X24" t="n">
         <v>350</v>
       </c>
       <c r="Y24" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25">
@@ -29274,7 +29274,7 @@
         <v>350</v>
       </c>
       <c r="J25" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K25" t="n">
         <v>350</v>
@@ -29304,7 +29304,7 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S26" t="n">
         <v>350</v>
@@ -29386,7 +29386,7 @@
         <v>350</v>
       </c>
       <c r="U26" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V26" t="n">
         <v>350</v>
@@ -29456,7 +29456,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
@@ -29465,16 +29465,16 @@
         <v>350</v>
       </c>
       <c r="U27" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
       </c>
       <c r="W27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="X27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>350</v>
@@ -29499,7 +29499,7 @@
         <v>350</v>
       </c>
       <c r="F28" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G28" t="n">
         <v>350</v>
@@ -29541,7 +29541,7 @@
         <v>350</v>
       </c>
       <c r="T28" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29617,7 +29617,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S29" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T29" t="n">
         <v>350</v>
@@ -29651,10 +29651,10 @@
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
@@ -29693,10 +29693,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S30" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T30" t="n">
         <v>350</v>
@@ -29824,7 +29824,7 @@
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T32" t="n">
         <v>350</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29900,7 +29900,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>217.1263858913485</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30109,7 +30109,7 @@
         <v>350</v>
       </c>
       <c r="Y35" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36">
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C36" t="n">
         <v>350</v>
@@ -30128,10 +30128,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>269.6305770343469</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
@@ -30188,7 +30188,7 @@
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30207,19 +30207,19 @@
         <v>350</v>
       </c>
       <c r="E37" t="n">
+        <v>350</v>
+      </c>
+      <c r="F37" t="n">
+        <v>350</v>
+      </c>
+      <c r="G37" t="n">
+        <v>350</v>
+      </c>
+      <c r="H37" t="n">
+        <v>350</v>
+      </c>
+      <c r="I37" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="F37" t="n">
-        <v>350</v>
-      </c>
-      <c r="G37" t="n">
-        <v>350</v>
-      </c>
-      <c r="H37" t="n">
-        <v>350</v>
-      </c>
-      <c r="I37" t="n">
-        <v>350</v>
       </c>
       <c r="J37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30359,7 +30359,7 @@
         <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30368,7 +30368,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>276.9584798124343</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>350</v>
+        <v>276.9584798124343</v>
       </c>
     </row>
     <row r="40">
@@ -30435,76 +30435,76 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>350</v>
+      </c>
+      <c r="C40" t="n">
+        <v>350</v>
+      </c>
+      <c r="D40" t="n">
+        <v>350</v>
+      </c>
+      <c r="E40" t="n">
+        <v>350</v>
+      </c>
+      <c r="F40" t="n">
+        <v>350</v>
+      </c>
+      <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="n">
+        <v>350</v>
+      </c>
+      <c r="M40" t="n">
+        <v>350</v>
+      </c>
+      <c r="N40" t="n">
+        <v>350</v>
+      </c>
+      <c r="O40" t="n">
+        <v>350</v>
+      </c>
+      <c r="P40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>350</v>
+      </c>
+      <c r="T40" t="n">
+        <v>350</v>
+      </c>
+      <c r="U40" t="n">
+        <v>350</v>
+      </c>
+      <c r="V40" t="n">
+        <v>350</v>
+      </c>
+      <c r="W40" t="n">
+        <v>350</v>
+      </c>
+      <c r="X40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Y40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C40" t="n">
-        <v>350</v>
-      </c>
-      <c r="D40" t="n">
-        <v>350</v>
-      </c>
-      <c r="E40" t="n">
-        <v>350</v>
-      </c>
-      <c r="F40" t="n">
-        <v>350</v>
-      </c>
-      <c r="G40" t="n">
-        <v>350</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
-      </c>
-      <c r="L40" t="n">
-        <v>350</v>
-      </c>
-      <c r="M40" t="n">
-        <v>350</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>350</v>
-      </c>
-      <c r="P40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>350</v>
-      </c>
-      <c r="R40" t="n">
-        <v>350</v>
-      </c>
-      <c r="S40" t="n">
-        <v>350</v>
-      </c>
-      <c r="T40" t="n">
-        <v>350</v>
-      </c>
-      <c r="U40" t="n">
-        <v>350</v>
-      </c>
-      <c r="V40" t="n">
-        <v>350</v>
-      </c>
-      <c r="W40" t="n">
-        <v>350</v>
-      </c>
-      <c r="X40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>350</v>
       </c>
     </row>
     <row r="41">
@@ -30532,7 +30532,7 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I41" t="n">
         <v>150.0811596826846</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30605,7 +30605,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
@@ -30641,13 +30641,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>276.9584798124344</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
       </c>
       <c r="T42" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="U42" t="n">
         <v>350</v>
@@ -30699,34 +30699,34 @@
         <v>350</v>
       </c>
       <c r="K43" t="n">
+        <v>350</v>
+      </c>
+      <c r="L43" t="n">
+        <v>350</v>
+      </c>
+      <c r="M43" t="n">
+        <v>350</v>
+      </c>
+      <c r="N43" t="n">
+        <v>350</v>
+      </c>
+      <c r="O43" t="n">
+        <v>350</v>
+      </c>
+      <c r="P43" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>350</v>
+      </c>
+      <c r="R43" t="n">
+        <v>350</v>
+      </c>
+      <c r="S43" t="n">
+        <v>350</v>
+      </c>
+      <c r="T43" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="L43" t="n">
-        <v>350</v>
-      </c>
-      <c r="M43" t="n">
-        <v>350</v>
-      </c>
-      <c r="N43" t="n">
-        <v>350</v>
-      </c>
-      <c r="O43" t="n">
-        <v>350</v>
-      </c>
-      <c r="P43" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>350</v>
-      </c>
-      <c r="R43" t="n">
-        <v>350</v>
-      </c>
-      <c r="S43" t="n">
-        <v>350</v>
-      </c>
-      <c r="T43" t="n">
-        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30769,10 +30769,10 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30887,13 +30887,13 @@
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
         <v>350</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>350</v>
@@ -30936,7 +30936,7 @@
         <v>350</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34755,16 +34755,16 @@
         <v>421</v>
       </c>
       <c r="N2" t="n">
-        <v>403.989898989899</v>
+        <v>421</v>
       </c>
       <c r="O2" t="n">
         <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="Q2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,31 +34877,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.14542695379679</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>153.7427098078749</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34995,13 +34995,13 @@
         <v>421</v>
       </c>
       <c r="O5" t="n">
+        <v>421</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>8.728168648832536</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>421</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.93132500843856</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35135,13 +35135,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>161.9037552066274</v>
       </c>
       <c r="J7" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35223,7 +35223,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>421</v>
@@ -35232,13 +35232,13 @@
         <v>421</v>
       </c>
       <c r="O8" t="n">
+        <v>421</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8.728168648832536</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35360,13 +35360,13 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>92.87826345571237</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>38.21745775415324</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
         <v>249.0416087255421</v>
@@ -35460,22 +35460,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="O11" t="n">
         <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>141.1524110730749</v>
+        <v>559</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35642,13 +35642,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W13" t="n">
         <v>123.6271901612903</v>
@@ -35694,10 +35694,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,13 +35706,13 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>20.40522350612631</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35831,7 +35831,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E16" t="n">
         <v>69.01909516304346</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35931,7 +35931,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35940,13 +35940,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>559</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36165,10 +36165,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>559</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>20.40522350612643</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,13 +36417,13 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36560,7 +36560,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J25" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K25" t="n">
         <v>61.47922619885696</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36785,7 +36785,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G28" t="n">
         <v>104.95612715847</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -36891,10 +36891,10 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -37116,7 +37116,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37128,13 +37128,13 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P32" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,7 +37353,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -37362,16 +37362,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
+        <v>184.1434931650599</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37493,7 +37493,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>61.23042579717762</v>
+        <v>69.01909516304346</v>
       </c>
       <c r="F37" t="n">
         <v>75.61714403225807</v>
@@ -37505,7 +37505,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I37" t="n">
-        <v>173.3665443798817</v>
+        <v>165.577875014016</v>
       </c>
       <c r="J37" t="n">
         <v>314.7310511640923</v>
@@ -37590,7 +37590,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -37599,7 +37599,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
         <v>77.27475335195533</v>
@@ -37790,7 +37790,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467183</v>
       </c>
     </row>
     <row r="41">
@@ -37827,7 +37827,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37836,13 +37836,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37985,7 +37985,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>20.40522350612654</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,13 +38076,13 @@
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38222,7 +38222,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
